--- a/Result/profitability/2712.xlsx
+++ b/Result/profitability/2712.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.185</v>
+        <v>-0.15</v>
       </c>
       <c r="N2" t="n">
-        <v>11.5175</v>
+        <v>14.78625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.225</v>
+        <v>-0.20125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.86125</v>
+        <v>17.6275</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.15125</v>
+        <v>-0.13625</v>
       </c>
       <c r="N4" t="n">
-        <v>17.32125</v>
+        <v>17.9225</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="N5" t="n">
-        <v>18.00375</v>
+        <v>18.32375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.17375</v>
+        <v>-0.21</v>
       </c>
       <c r="N6" t="n">
-        <v>17.58</v>
+        <v>15.92375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.19125</v>
+        <v>-0.16625</v>
       </c>
       <c r="N7" t="n">
-        <v>16.93625</v>
+        <v>18.99625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8814,6 +8814,133 @@
       </c>
       <c r="AM66" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>132</v>
+      </c>
+      <c r="D67" t="n">
+        <v>107</v>
+      </c>
+      <c r="E67" t="n">
+        <v>26</v>
+      </c>
+      <c r="F67" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-7.02%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-0.15125</v>
+      </c>
+      <c r="N67" t="n">
+        <v>12.5125</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.2153652392947103</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.07999999999999999</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.5333333333333332</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>2.560000000000002</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.1529271206690563</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
